--- a/forms/trg/Formulir_TRG_locwis.xlsx
+++ b/forms/trg/Formulir_TRG_locwis.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B18)</f>
+        <f>COUNTA(Anggota!B5:B19)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F18)</f>
+        <f>COUNTA(Anggota!F5:F19)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,27 +913,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>Prof. Dr. Muhammad Hasyim, M.Si.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Graduate Student</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6057163</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>54881598200</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,7 +950,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Taqdir</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -977,10 +981,22 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Taqdir</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D7" s="12" t="n"/>
-      <c r="E7" s="11" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Graduate Student</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
@@ -988,7 +1004,11 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1177,15 +1197,32 @@
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
